--- a/ProyectoSoftwareSistemas/bin/Debug/output/EXA2_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/EXA2_ArchivoIntermedio.xlsx
@@ -83,7 +83,7 @@
     <x:t>Inmediato</x:t>
   </x:si>
   <x:si>
-    <x:t>69101039*</x:t>
+    <x:t>69101038*</x:t>
   </x:si>
   <x:si>
     <x:t>0004</x:t>
@@ -110,10 +110,7 @@
     <x:t>3</x:t>
   </x:si>
   <x:si>
-    <x:t>Error: Operando fuera de rango</x:t>
-  </x:si>
-  <x:si>
-    <x:t>756FFF</x:t>
+    <x:t>754005</x:t>
   </x:si>
   <x:si>
     <x:t>0007</x:t>
@@ -146,7 +143,7 @@
     <x:t>Simple</x:t>
   </x:si>
   <x:si>
-    <x:t>532029</x:t>
+    <x:t>532028</x:t>
   </x:si>
   <x:si>
     <x:t>000D</x:t>
@@ -161,7 +158,7 @@
     <x:t>Indirecto</x:t>
   </x:si>
   <x:si>
-    <x:t>566FFF</x:t>
+    <x:t>564000</x:t>
   </x:si>
   <x:si>
     <x:t>0010</x:t>
@@ -188,15 +185,12 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
+    <x:t>Error: Sintaxis</x:t>
+  </x:si>
+  <x:si>
     <x:t>F0</x:t>
   </x:si>
   <x:si>
-    <x:t>Error de sintaxis</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0014</x:t>
-  </x:si>
-  <x:si>
     <x:t>LDS</x:t>
   </x:si>
   <x:si>
@@ -206,7 +200,7 @@
     <x:t>6D6FFF</x:t>
   </x:si>
   <x:si>
-    <x:t>0017</x:t>
+    <x:t>0016</x:t>
   </x:si>
   <x:si>
     <x:t>CICLO</x:t>
@@ -218,7 +212,7 @@
     <x:t>53A01C</x:t>
   </x:si>
   <x:si>
-    <x:t>001A</x:t>
+    <x:t>0019</x:t>
   </x:si>
   <x:si>
     <x:t>+AND</x:t>
@@ -227,13 +221,10 @@
     <x:t>#1000H</x:t>
   </x:si>
   <x:si>
-    <x:t>Símbolo no encontrado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>417FFFFF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>001E</x:t>
+    <x:t>41101000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>001D</x:t>
   </x:si>
   <x:si>
     <x:t>RMO</x:t>
@@ -251,13 +242,13 @@
     <x:t>AC05</x:t>
   </x:si>
   <x:si>
-    <x:t>0020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>526FFF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0023</x:t>
+    <x:t>001F</x:t>
+  </x:si>
+  <x:si>
+    <x:t>524000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0022</x:t>
   </x:si>
   <x:si>
     <x:t>COMPR</x:t>
@@ -269,7 +260,7 @@
     <x:t>A050</x:t>
   </x:si>
   <x:si>
-    <x:t>0025</x:t>
+    <x:t>0024</x:t>
   </x:si>
   <x:si>
     <x:t>JGT</x:t>
@@ -281,7 +272,7 @@
     <x:t>372003</x:t>
   </x:si>
   <x:si>
-    <x:t>0028</x:t>
+    <x:t>0027</x:t>
   </x:si>
   <x:si>
     <x:t>J</x:t>
@@ -293,16 +284,16 @@
     <x:t>3F6FFF</x:t>
   </x:si>
   <x:si>
-    <x:t>002B</x:t>
+    <x:t>002A</x:t>
   </x:si>
   <x:si>
     <x:t>MAX</x:t>
   </x:si>
   <x:si>
-    <x:t>576FFF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>002E</x:t>
+    <x:t>574005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>002D</x:t>
   </x:si>
   <x:si>
     <x:t>AVANZA</x:t>
@@ -317,7 +308,7 @@
     <x:t>B840</x:t>
   </x:si>
   <x:si>
-    <x:t>0030</x:t>
+    <x:t>002F</x:t>
   </x:si>
   <x:si>
     <x:t>JLT</x:t>
@@ -326,7 +317,7 @@
     <x:t>3B2FE4</x:t>
   </x:si>
   <x:si>
-    <x:t>0033</x:t>
+    <x:t>0032</x:t>
   </x:si>
   <x:si>
     <x:t>RSUB</x:t>
@@ -335,7 +326,7 @@
     <x:t>4F0000</x:t>
   </x:si>
   <x:si>
-    <x:t>0036</x:t>
+    <x:t>0035</x:t>
   </x:si>
   <x:si>
     <x:t>BYTE</x:t>
@@ -347,7 +338,7 @@
     <x:t>0F3224</x:t>
   </x:si>
   <x:si>
-    <x:t>0039</x:t>
+    <x:t>0038</x:t>
   </x:si>
   <x:si>
     <x:t>RESB</x:t>
@@ -356,13 +347,13 @@
     <x:t>1000H</x:t>
   </x:si>
   <x:si>
-    <x:t>1039</x:t>
+    <x:t>1038</x:t>
   </x:si>
   <x:si>
     <x:t>RESW</x:t>
   </x:si>
   <x:si>
-    <x:t>103C</x:t>
+    <x:t>103B</x:t>
   </x:si>
   <x:si>
     <x:t>A</x:t>
@@ -371,12 +362,12 @@
     <x:t>AC00</x:t>
   </x:si>
   <x:si>
+    <x:t>103D</x:t>
+  </x:si>
+  <x:si>
     <x:t>103E</x:t>
   </x:si>
   <x:si>
-    <x:t>103F</x:t>
-  </x:si>
-  <x:si>
     <x:t>MAIN</x:t>
   </x:si>
   <x:si>
@@ -386,7 +377,7 @@
     <x:t>4B100000*</x:t>
   </x:si>
   <x:si>
-    <x:t>1043</x:t>
+    <x:t>1042</x:t>
   </x:si>
   <x:si>
     <x:t>CLEAR</x:t>
@@ -395,7 +386,7 @@
     <x:t>B400</x:t>
   </x:si>
   <x:si>
-    <x:t>1045</x:t>
+    <x:t>1044</x:t>
   </x:si>
   <x:si>
     <x:t>Error: Símbolo duplicado</x:t>
@@ -404,7 +395,7 @@
     <x:t>532FF6</x:t>
   </x:si>
   <x:si>
-    <x:t>1048</x:t>
+    <x:t>1047</x:t>
   </x:si>
   <x:si>
     <x:t>C'F2'</x:t>
@@ -413,34 +404,34 @@
     <x:t>4632</x:t>
   </x:si>
   <x:si>
-    <x:t>104A</x:t>
+    <x:t>1049</x:t>
   </x:si>
   <x:si>
     <x:t>END</x:t>
   </x:si>
   <x:si>
-    <x:t>HEXA2  00000000104A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T0000001E69101039756FFF87EFFF532029566FFF050001F06D6FFF53A01C417FFFFF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00001E1BAC05526FFFA0503720033F6FFF576FFFB8403B2FE44F00000F3224</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00103C02AC00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00103F0B4B100000B400532FF64632</x:t>
+    <x:t>HEXA2  000000001049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T0000001E6910103875400587EFFF532028564000050001F06D6FFF53A01C41101000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00001D1BAC05524000A0503720033F6FFF574005B8403B2FE44F00000F3224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00103B02AC00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00103E0B4B100000B400532FF64632</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">M00000105+EXA2  </x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">M00104005+EXA2  </x:t>
-  </x:si>
-  <x:si>
-    <x:t>E00103F</x:t>
+    <x:t xml:space="preserve">M00103F05+EXA2  </x:t>
+  </x:si>
+  <x:si>
+    <x:t>E00103E</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -791,7 +782,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I34"/>
+  <x:dimension ref="A1:I33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -962,10 +953,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -973,28 +964,28 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="E7" s="0" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H7" s="0" t="s">
+      <x:c r="I7" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -1002,28 +993,28 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="E8" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -1031,28 +1022,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="E9" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -1060,16 +1051,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
+      <x:c r="E10" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>30</x:v>
@@ -1081,7 +1072,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -1089,25 +1080,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="s">
+      <x:c r="D11" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D11" s="0" t="s">
+      <x:c r="E11" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
         <x:v>57</x:v>
@@ -1115,248 +1106,248 @@
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="H16" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I16" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
         <x:v>90</x:v>
@@ -1365,10 +1356,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
         <x:v>91</x:v>
@@ -1376,54 +1367,54 @@
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>15</x:v>
@@ -1434,7 +1425,7 @@
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>100</x:v>
@@ -1446,13 +1437,13 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
         <x:v>15</x:v>
@@ -1463,48 +1454,48 @@
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>13</x:v>
@@ -1516,24 +1507,24 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>13</x:v>
@@ -1550,112 +1541,112 @@
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
+      <x:c r="F27" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H27" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
         <x:v>15</x:v>
@@ -1666,28 +1657,28 @@
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F31" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G31" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H31" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
         <x:v>125</x:v>
@@ -1695,28 +1686,28 @@
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>126</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
         <x:v>128</x:v>
@@ -1724,7 +1715,7 @@
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>129</x:v>
@@ -1733,10 +1724,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>13</x:v>
@@ -1748,35 +1739,6 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:9">
-      <x:c r="A34" s="0">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G34" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H34" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I34" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
@@ -1802,42 +1764,42 @@
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
       <x:c r="A7" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:1">
       <x:c r="A8" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/ProyectoSoftwareSistemas/bin/Debug/output/EXA2_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/EXA2_ArchivoIntermedio.xlsx
@@ -110,7 +110,7 @@
     <x:t>3</x:t>
   </x:si>
   <x:si>
-    <x:t>754005</x:t>
+    <x:t>754003</x:t>
   </x:si>
   <x:si>
     <x:t>0007</x:t>
@@ -188,9 +188,6 @@
     <x:t>Error: Sintaxis</x:t>
   </x:si>
   <x:si>
-    <x:t>F0</x:t>
-  </x:si>
-  <x:si>
     <x:t>LDS</x:t>
   </x:si>
   <x:si>
@@ -290,7 +287,7 @@
     <x:t>MAX</x:t>
   </x:si>
   <x:si>
-    <x:t>574005</x:t>
+    <x:t>574003</x:t>
   </x:si>
   <x:si>
     <x:t>002D</x:t>
@@ -359,13 +356,10 @@
     <x:t>A</x:t>
   </x:si>
   <x:si>
-    <x:t>AC00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>103D</x:t>
-  </x:si>
-  <x:si>
-    <x:t>103E</x:t>
+    <x:t>Error: Falta registro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>103C</x:t>
   </x:si>
   <x:si>
     <x:t>MAIN</x:t>
@@ -377,61 +371,58 @@
     <x:t>4B100000*</x:t>
   </x:si>
   <x:si>
+    <x:t>1040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B400</x:t>
+  </x:si>
+  <x:si>
     <x:t>1042</x:t>
   </x:si>
   <x:si>
-    <x:t>CLEAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1044</x:t>
-  </x:si>
-  <x:si>
     <x:t>Error: Símbolo duplicado</x:t>
   </x:si>
   <x:si>
     <x:t>532FF6</x:t>
   </x:si>
   <x:si>
+    <x:t>1045</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C'F2'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4632</x:t>
+  </x:si>
+  <x:si>
     <x:t>1047</x:t>
   </x:si>
   <x:si>
-    <x:t>C'F2'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1049</x:t>
-  </x:si>
-  <x:si>
     <x:t>END</x:t>
   </x:si>
   <x:si>
-    <x:t>HEXA2  000000001049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T0000001E6910103875400587EFFF532028564000050001F06D6FFF53A01C41101000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00001D1BAC05524000A0503720033F6FFF574005B8403B2FE44F00000F3224</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00103B02AC00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00103E0B4B100000B400532FF64632</x:t>
+    <x:t>HEXA2  000000001047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T0000001D6910103875400387EFFF5320285640000500016D6FFF53A01C41101000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00001D1BAC05524000A0503720033F6FFF574003B8403B2FE44F00000F3224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00103C0B4B100000B400532FF64632</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">M00000105+EXA2  </x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">M00103F05+EXA2  </x:t>
-  </x:si>
-  <x:si>
-    <x:t>E00103E</x:t>
+    <x:t xml:space="preserve">M00103D05+EXA2  </x:t>
+  </x:si>
+  <x:si>
+    <x:t>E00103C</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1101,7 +1092,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -1115,10 +1106,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>30</x:v>
@@ -1130,7 +1121,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -1138,16 +1129,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>30</x:v>
@@ -1159,7 +1150,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -1167,16 +1158,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
+      <x:c r="E14" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>20</x:v>
@@ -1188,7 +1179,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -1196,28 +1187,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
+      <x:c r="E15" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E15" s="0" t="s">
+      <x:c r="F15" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="F15" s="0" t="s">
+      <x:c r="G15" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G15" s="0" t="s">
+      <x:c r="H15" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I15" s="0" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -1225,7 +1216,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>15</x:v>
@@ -1246,7 +1237,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1254,28 +1245,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
+      <x:c r="E17" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="E17" s="0" t="s">
+      <x:c r="F17" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G17" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I17" s="0" t="s">
-        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1283,16 +1274,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
+      <x:c r="E18" s="0" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>30</x:v>
@@ -1304,7 +1295,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1312,16 +1303,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
+      <x:c r="E19" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>30</x:v>
@@ -1333,7 +1324,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1341,16 +1332,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>30</x:v>
@@ -1362,7 +1353,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1370,28 +1361,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C21" s="0" t="s">
+      <x:c r="D21" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D21" s="0" t="s">
+      <x:c r="E21" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="E21" s="0" t="s">
+      <x:c r="F21" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H21" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I21" s="0" t="s">
-        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1399,16 +1390,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>30</x:v>
@@ -1420,7 +1411,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1428,13 +1419,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
         <x:v>15</x:v>
@@ -1449,7 +1440,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1457,16 +1448,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>13</x:v>
@@ -1478,7 +1469,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1486,16 +1477,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
+      <x:c r="E25" s="0" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>109</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>13</x:v>
@@ -1515,13 +1506,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
         <x:v>55</x:v>
@@ -1544,28 +1535,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
+      <x:c r="F27" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H27" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1573,13 +1564,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
         <x:v>55</x:v>
@@ -1602,13 +1593,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>118</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
         <x:v>17</x:v>
@@ -1623,7 +1614,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1631,28 +1622,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F30" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G30" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H30" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I30" s="0" t="s">
-        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1660,16 +1651,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>30</x:v>
@@ -1678,10 +1669,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1689,16 +1680,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>13</x:v>
@@ -1710,7 +1701,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1718,16 +1709,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>13</x:v>
@@ -1756,50 +1747,45 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:A8"/>
+  <x:dimension ref="A1:A7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="74.567768" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="72.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
       <x:c r="A7" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:1">
-      <x:c r="A8" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
